--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ULACIA ZKE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ULACIA ZKE.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>86.1927</v>
+        <v>50.8905</v>
       </c>
       <c r="E2" t="n">
-        <v>30.232</v>
+        <v>7.168900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>55.9605</v>
+        <v>43.7216</v>
       </c>
       <c r="G2" t="n">
         <v>26.2801</v>
@@ -610,13 +610,13 @@
         <v>49.2173</v>
       </c>
       <c r="S2" t="n">
-        <v>72.3805</v>
+        <v>37.0779</v>
       </c>
       <c r="T2" t="n">
-        <v>36.2088</v>
+        <v>13.1454</v>
       </c>
       <c r="U2" t="n">
-        <v>36.1718</v>
+        <v>23.9326</v>
       </c>
       <c r="V2" t="n">
         <v>-8.2216</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>32.0115</v>
+        <v>30.7854</v>
       </c>
       <c r="E3" t="n">
-        <v>13.7551</v>
+        <v>8.698600000000003</v>
       </c>
       <c r="F3" t="n">
-        <v>18.2563</v>
+        <v>22.0865</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0413</v>
+        <v>10.9439</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9467</v>
+        <v>12.2629</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.9053</v>
+        <v>-1.3194</v>
       </c>
       <c r="J3" t="n">
-        <v>27.2564</v>
+        <v>25.7332</v>
       </c>
       <c r="K3" t="n">
-        <v>22.0097</v>
+        <v>23.6489</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2472</v>
+        <v>2.0842</v>
       </c>
       <c r="M3" t="n">
-        <v>-23.2155</v>
+        <v>-14.7893</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.0629</v>
+        <v>-11.3859</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.152200000000001</v>
+        <v>-3.4035</v>
       </c>
       <c r="P3" t="n">
-        <v>2.702000000000001</v>
+        <v>-40.7243</v>
       </c>
       <c r="Q3" t="n">
-        <v>-38.9874</v>
+        <v>-85.5025</v>
       </c>
       <c r="R3" t="n">
-        <v>41.6899</v>
+        <v>44.778</v>
       </c>
       <c r="S3" t="n">
-        <v>26.4473</v>
+        <v>10.8886</v>
       </c>
       <c r="T3" t="n">
-        <v>12.5699</v>
+        <v>-0.4049</v>
       </c>
       <c r="U3" t="n">
-        <v>13.8771</v>
+        <v>11.2937</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1795</v>
+        <v>49.6774</v>
       </c>
       <c r="W3" t="n">
-        <v>12.9161</v>
+        <v>68.8733</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.0958</v>
+        <v>-19.1959</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>17.1953</v>
+        <v>25.7666</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.872499999999999</v>
+        <v>2.283799999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>19.068</v>
+        <v>23.4826</v>
       </c>
       <c r="G4" t="n">
         <v>29.5327</v>
@@ -766,13 +766,13 @@
         <v>30.1091</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.7736</v>
+        <v>4.7977</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.827</v>
+        <v>-1.6703</v>
       </c>
       <c r="U4" t="n">
-        <v>2.0532</v>
+        <v>6.4683</v>
       </c>
       <c r="V4" t="n">
         <v>4.3673</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>16.177</v>
+        <v>19.6447</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.489800000000002</v>
+        <v>6.235699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>18.6663</v>
+        <v>13.4088</v>
       </c>
       <c r="G5" t="n">
-        <v>10.9439</v>
+        <v>4.0413</v>
       </c>
       <c r="H5" t="n">
-        <v>12.2629</v>
+        <v>6.9467</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3194</v>
+        <v>-2.9053</v>
       </c>
       <c r="J5" t="n">
-        <v>25.7332</v>
+        <v>27.2564</v>
       </c>
       <c r="K5" t="n">
-        <v>23.6489</v>
+        <v>22.0097</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0842</v>
+        <v>5.2472</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.7893</v>
+        <v>-23.2155</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.3859</v>
+        <v>-15.0629</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.4035</v>
+        <v>-8.152200000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-40.7243</v>
+        <v>2.702000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-85.5025</v>
+        <v>-38.9874</v>
       </c>
       <c r="R5" t="n">
-        <v>44.778</v>
+        <v>41.6899</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.7196</v>
+        <v>14.0803</v>
       </c>
       <c r="T5" t="n">
-        <v>-11.5931</v>
+        <v>5.050599999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>7.8736</v>
+        <v>9.0296</v>
       </c>
       <c r="V5" t="n">
-        <v>49.6774</v>
+        <v>-1.1795</v>
       </c>
       <c r="W5" t="n">
-        <v>68.8733</v>
+        <v>12.9161</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.1959</v>
+        <v>-14.0958</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>9.868500000000001</v>
+        <v>7.236599999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>8.323499999999999</v>
+        <v>3.911099999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5451</v>
+        <v>3.325399999999999</v>
       </c>
       <c r="G6" t="n">
         <v>17.0288</v>
@@ -922,13 +922,13 @@
         <v>33.7764</v>
       </c>
       <c r="S6" t="n">
-        <v>13.7765</v>
+        <v>11.1445</v>
       </c>
       <c r="T6" t="n">
-        <v>7.951</v>
+        <v>3.5388</v>
       </c>
       <c r="U6" t="n">
-        <v>5.8253</v>
+        <v>7.605700000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-16.1111</v>
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>4.7149</v>
+        <v>0.2427</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9865</v>
+        <v>-1.2806</v>
       </c>
       <c r="F7" t="n">
-        <v>2.728599999999999</v>
+        <v>1.5233</v>
       </c>
       <c r="G7" t="n">
         <v>0.3033999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>5.4041</v>
       </c>
       <c r="S7" t="n">
-        <v>10.3028</v>
+        <v>5.8306</v>
       </c>
       <c r="T7" t="n">
-        <v>6.9207</v>
+        <v>3.6538</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3821</v>
+        <v>2.1769</v>
       </c>
       <c r="V7" t="n">
         <v>-5.119300000000001</v>
@@ -1033,13 +1033,13 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1363</v>
+        <v>-0.9615999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>6.5626</v>
+        <v>2.7166</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.4263</v>
+        <v>-3.6783</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7299999999999998</v>
@@ -1078,13 +1078,13 @@
         <v>5.404</v>
       </c>
       <c r="S8" t="n">
-        <v>6.2544</v>
+        <v>3.1566</v>
       </c>
       <c r="T8" t="n">
-        <v>5.7479</v>
+        <v>1.9021</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5062</v>
+        <v>1.2543</v>
       </c>
       <c r="V8" t="n">
         <v>-6.6694</v>
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1563</v>
+        <v>-1.0095</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3277</v>
+        <v>-1.1274</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1714</v>
+        <v>0.1179</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1801</v>
@@ -1156,13 +1156,13 @@
         <v>1.351</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1693</v>
+        <v>-0.0225</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2975</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1282</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>-13.4539</v>
+        <v>-2.894299999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.974300000000001</v>
+        <v>-15.6822</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.4793</v>
+        <v>12.7877</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2547</v>
+        <v>0.7302999999999993</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3524</v>
+        <v>-5.992699999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>4.902600000000001</v>
+        <v>6.723400000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>14.525</v>
+        <v>15.1871</v>
       </c>
       <c r="K10" t="n">
-        <v>8.6401</v>
+        <v>8.795399999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>5.8851</v>
+        <v>6.3915</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.270300000000001</v>
+        <v>-14.4566</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.2877</v>
+        <v>-14.7881</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9824999999999999</v>
+        <v>0.3316999999999998</v>
       </c>
       <c r="P10" t="n">
-        <v>-11.9663</v>
+        <v>-19.4937</v>
       </c>
       <c r="Q10" t="n">
-        <v>-29.5298</v>
+        <v>-50.761</v>
       </c>
       <c r="R10" t="n">
-        <v>17.5634</v>
+        <v>31.2674</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7876</v>
+        <v>4.5462</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7587</v>
+        <v>1.356</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9711000000000001</v>
+        <v>3.1905</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.5291</v>
+        <v>11.323</v>
       </c>
       <c r="W10" t="n">
-        <v>5.2727</v>
+        <v>18.5366</v>
       </c>
       <c r="X10" t="n">
-        <v>-15.8018</v>
+        <v>-7.2139</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.3651</v>
+        <v>-9.446099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.8588</v>
+        <v>-10.5544</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4935000000000004</v>
+        <v>1.1082</v>
       </c>
       <c r="G11" t="n">
         <v>7.209300000000001</v>
@@ -1312,13 +1312,13 @@
         <v>15.633</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.0511</v>
+        <v>1.8675</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.3401</v>
+        <v>-1.0355</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2888</v>
+        <v>2.9029</v>
       </c>
       <c r="V11" t="n">
         <v>-4.4337</v>
@@ -1345,13 +1345,13 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.5519</v>
+        <v>-10.4111</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.2702</v>
+        <v>-15.7869</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7181</v>
+        <v>5.3759</v>
       </c>
       <c r="G12" t="n">
         <v>-9.9582</v>
@@ -1390,13 +1390,13 @@
         <v>16.4055</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7948</v>
+        <v>2.3461</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.0544</v>
+        <v>-0.5714999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2596</v>
+        <v>2.9173</v>
       </c>
       <c r="V12" t="n">
         <v>-5.115399999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.1532</v>
+        <v>-11.7632</v>
       </c>
       <c r="E13" t="n">
-        <v>-27.7334</v>
+        <v>-6.959800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5807</v>
+        <v>-4.8036</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7302999999999993</v>
+        <v>6.2547</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.992699999999999</v>
+        <v>1.3524</v>
       </c>
       <c r="I13" t="n">
-        <v>6.723400000000001</v>
+        <v>4.902600000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>15.1871</v>
+        <v>14.525</v>
       </c>
       <c r="K13" t="n">
-        <v>8.795399999999999</v>
+        <v>8.6401</v>
       </c>
       <c r="L13" t="n">
-        <v>6.3915</v>
+        <v>5.8851</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.4566</v>
+        <v>-8.270300000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.7881</v>
+        <v>-7.2877</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3316999999999998</v>
+        <v>-0.9824999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-19.4937</v>
+        <v>-11.9663</v>
       </c>
       <c r="Q13" t="n">
-        <v>-50.761</v>
+        <v>-29.5298</v>
       </c>
       <c r="R13" t="n">
-        <v>31.2674</v>
+        <v>17.5634</v>
       </c>
       <c r="S13" t="n">
-        <v>-13.7122</v>
+        <v>4.477799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-10.6956</v>
+        <v>2.7731</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0163</v>
+        <v>1.7044</v>
       </c>
       <c r="V13" t="n">
-        <v>11.323</v>
+        <v>-10.5291</v>
       </c>
       <c r="W13" t="n">
-        <v>18.5366</v>
+        <v>5.2727</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.2139</v>
+        <v>-15.8018</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-28.1877</v>
+        <v>-15.0611</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.1858</v>
+        <v>-12.1853</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.001199999999999</v>
+        <v>-2.875800000000001</v>
       </c>
       <c r="G14" t="n">
         <v>2.007499999999999</v>
@@ -1546,13 +1546,13 @@
         <v>32.4255</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.3752</v>
+        <v>6.7514</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.1275</v>
+        <v>-0.1265999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7521999999999996</v>
+        <v>6.877899999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-18.4158</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-31.1172</v>
+        <v>-18.5399</v>
       </c>
       <c r="E15" t="n">
-        <v>-25.729</v>
+        <v>-18.5843</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.388199999999999</v>
+        <v>0.04450000000000021</v>
       </c>
       <c r="G15" t="n">
         <v>0.3776999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>34.9343</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.0869</v>
+        <v>4.4902</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.6464</v>
+        <v>0.4981</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4407</v>
+        <v>3.992</v>
       </c>
       <c r="V15" t="n">
         <v>-11.6344</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>42.3109</v>
+        <v>64.47970000000002</v>
       </c>
       <c r="E16" t="n">
-        <v>-58.58180000000002</v>
+        <v>-51.1462</v>
       </c>
       <c r="F16" t="n">
-        <v>100.8935</v>
+        <v>115.6247</v>
       </c>
       <c r="G16" t="n">
         <v>92.84139999999999</v>
@@ -1672,7 +1672,7 @@
         <v>34.8564</v>
       </c>
       <c r="I16" t="n">
-        <v>57.98519999999999</v>
+        <v>57.98519999999998</v>
       </c>
       <c r="J16" t="n">
         <v>230.9317</v>
@@ -1696,25 +1696,25 @@
         <v>-117.7345</v>
       </c>
       <c r="Q16" t="n">
-        <v>-477.6929000000001</v>
+        <v>-477.6929</v>
       </c>
       <c r="R16" t="n">
         <v>359.9589</v>
       </c>
       <c r="S16" t="n">
-        <v>89.26639999999999</v>
+        <v>111.4329</v>
       </c>
       <c r="T16" t="n">
-        <v>20.5754</v>
+        <v>28.012</v>
       </c>
       <c r="U16" t="n">
-        <v>68.68999999999998</v>
+        <v>83.42080000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-22.0616</v>
       </c>
       <c r="W16" t="n">
-        <v>167.6078</v>
+        <v>167.6078000000001</v>
       </c>
       <c r="X16" t="n">
         <v>-189.6702</v>
